--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -612,7 +612,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Booth scanner — booth-a03@natcon.id (Kopi Nusantara) · booth-sp01@natcon.id (BNI Xpora, sponsor)</t>
+          <t>Booth scanner — booth-a1@natcon.id (SSCX International) · booth-sp01@natcon.id (BNI Xpora, sponsor)</t>
         </is>
       </c>
     </row>
@@ -670,6 +670,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -783,12 +784,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Sign in as booth-a03@natcon.id / natcon2026.</t>
+          <t>Sign in as booth-a1@natcon.id / natcon2026.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Lands on Booth Scanner titled 'Kopi Nusantara · Booth A-03'. Bottom nav shows Scanner and Dashboard only.</t>
+          <t>Lands on Booth Scanner titled 'SSCX International · Booth A1'. Bottom nav shows Scanner and Dashboard only.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
@@ -1296,6 +1297,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2009,6 +2011,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2267,7 +2270,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Type a booth QR payload (BOOTH:A-03) into manual input.</t>
+          <t>Type a booth QR payload (BOOTH:A1) into manual input.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2490,6 +2493,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3261,6 +3265,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3800,6 +3805,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4223,6 +4229,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4699,12 +4706,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>booth-a03@natcon.id / natcon2026</t>
+          <t>booth-a1@natcon.id / natcon2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Kopi Nusantara · booth A-03</t>
+          <t>SSCX International · booth A1 (from the official Data Booth sheet)</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4745,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>A-03 → booth-a03, SP-01 → booth-sp01</t>
+          <t>A1 → booth-a1, SP-01 → booth-sp01</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4825,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>BOOTH:A-03</t>
+          <t>BOOTH:A1</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -670,7 +670,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -784,12 +783,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Sign in as booth-a1@natcon.id / natcon2026.</t>
+          <t>Open the booth door at /tenant/login. Sign in as booth-a1@natcon.id / natcon2026.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Lands on Booth Scanner titled 'SSCX International · Booth A1'. Bottom nav shows Scanner and Dashboard only.</t>
+          <t>The page is headed 'Booth Scanner' and shows no 'Forgot your password?'. After sign-in: Booth Scanner titled 'SSCX International · Booth A1', bottom nav Scanner and Dashboard only.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
@@ -1258,13 +1257,103 @@
       </c>
       <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>AUTH-20</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Open /login and read the page.</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Headed 'Welcome to' with attendee wording, a 'Forgot your password?' link, and a link across to the booth sign-in.</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr"/>
+      <c r="G23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>AUTH-21</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Open /tenant/login and sign in with an ATTENDEE account.</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Still works — you land on the attendee home. The wrong door must never lock someone out.</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr"/>
+      <c r="G24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>AUTH-22</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Signed in as a booth</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Press Log out.</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Returns to the BOOTH sign-in (/tenant/login), not the attendee one.</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F4:F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1297,7 +1386,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2011,7 +2099,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2493,7 +2580,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3265,7 +3351,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3805,7 +3890,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4229,7 +4313,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4605,7 +4688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4877,6 +4960,40 @@
       </c>
       <c r="C16" s="11" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Attendee sign-in</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>http://localhost:5173/login</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>The door printed on the attendee ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Booth sign-in</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>http://localhost:5173/tenant/login</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>The door given to booth and sponsor crews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -2561,7 +2561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3313,12 +3313,239 @@
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>MD-25</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Breakout Classes</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Read the Quota column for a class nobody has registered for.</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Shows taken/quota (e.g. 0/60), an empty fill bar and 'N seats left'.</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>MD-26</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Breakout Classes</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Click the quota number, type 45, press Enter.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Saves without opening the edit form; the row shows 0/45 and '45 seats left'. Re-open the class in Edit: description, cover and speaker photos are untouched.</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>MD-27</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Breakout Classes</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Click the quota number, change it, press Esc.</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>The editor closes and the old quota stays — nothing was saved.</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>MD-28</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>A class with 3 attendees registered</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Set its quota to 2.</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Refused, with '3 already registered — cancel registrations first'. The old quota is still in place after a page reload.</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>MD-29</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Same class, 3 registered</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Set its quota to exactly 3.</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Accepted. The row reads 3/3 with a full bar and FULL in red.</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>MD-30</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>A class showing FULL</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Register one more attendee into it (Detail → register by code/email/phone).</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Refused: 'this seminar is fully booked'. An attendee picking it in the app is turned away too.</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>MD-31</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Breakout Classes</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Open Edit on a class with registrations and set Quota below that count.</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>The full edit form refuses it exactly like the quota cell does.</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>MD-32</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Breakout Classes</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Set a quota of 0 or a negative number.</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Refused — the quota must be at least 1.</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F4:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -3559,7 +3559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Lucky Draw, several attendees hold pins</t>
+          <t>Lucky Draw, attendee list imported</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Shows the eligible count. It must equal the number of attendees with at least one pin — check against the Attendee Pins report.</t>
+          <t>Shows the eligible count. It must equal the TOTAL number of registered attendees — pins do not decide eligibility. Check against Master Data → Attendees.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -4078,6 +4078,34 @@
       </c>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>OPS-24</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Lucky Draw</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Press Stage mode, then Space, then Esc.</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Space draws one winner (never two, however fast you press). Esc returns to the panel and the page is where you left it.</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -591,28 +591,24 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Accounts (seeded, password: natcon2026)</t>
+          <t>Accounts — a fresh database has ONE login</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Admin — admin@natcon.id</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Attendee — reddie@natcon.id (NATCON-2026-08154) · sinta@natcon.id (…-08201) · agus@natcon.id (…-08322)</t>
+          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). Everything else is created from there: import the attendee sheet (Data Peserta) and the booth sheet (Data Booth), then generate the networking tables on the Tables page.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Booth scanner — booth-a1@natcon.id (SSCX International) · booth-sp01@natcon.id (BNI Xpora, sponsor)</t>
+          <t>Attendee — any email from the imported sheet; first password = chapter + first name, lowercase without spaces. Booth — booth-&lt;code&gt;@natcon.id / SEED_PASSWORD, created automatically with each booth.</t>
         </is>
       </c>
     </row>
@@ -749,17 +745,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Seeded attendee</t>
+          <t>Attendee from the imported sheet</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>On the attendee app sign in as reddie@natcon.id / natcon2026.</t>
+          <t>On the attendee app sign in with an attendee's email and their generated password (chapter + first name, lowercase, no spaces).</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Lands on Home: 'Hello, Reddie', member pass card with a QR and the member ID NATCON-2026-08154.</t>
+          <t>Asked to choose a password on this first sign-in, then lands on Home: 'Hello, &lt;first name&gt;', member pass card with a QR and their member ID.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
@@ -783,7 +779,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Open the booth door at /tenant/login. Sign in as booth-a1@natcon.id / natcon2026.</t>
+          <t>Open the booth door at /tenant/login. Sign in as booth-&lt;code&gt;@natcon.id with SEED_PASSWORD.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -4988,68 +4984,68 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Attendee 1</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>reddie@natcon.id / natcon2026</t>
+          <t>admin@natcon.id / SEED_PASSWORD</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>NATCON-2026-08154 · BNI Chapter Jakarta Elite · +62811000154</t>
+          <t>The only account a fresh database has</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Attendee 2</t>
+          <t>Attendees</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>sinta@natcon.id / natcon2026</t>
+          <t>import Data Peserta.xlsx</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>NATCON-2026-08201 · BNI Chapter Jakarta Elite · +62811000201</t>
+          <t>769 rows; password = chapter + first name, then they set their own</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Attendee 3</t>
+          <t>Booths &amp; sponsors</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>agus@natcon.id / natcon2026</t>
+          <t>import Data Booth.xlsx</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>NATCON-2026-08322 · BNI Chapter Bandung Raya · +62811000322</t>
+          <t>each booth gets booth-&lt;code&gt;@natcon.id on SEED_PASSWORD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Booth scanner</t>
+          <t>Networking tables</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>booth-a1@natcon.id / natcon2026</t>
+          <t>Tables page → Generate</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>SSCX International · booth A1 (from the official Data Booth sheet)</t>
+          <t>none exist until the committee makes them</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5079,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>A1 → booth-a1, SP-01 → booth-sp01</t>
+          <t>Booth login pattern: A1 → booth-a1@natcon.id, SP-01 → booth-sp01@natcon.id</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -601,14 +601,14 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). Everything else is created from there: import the attendee sheet (Data Peserta) and the booth sheet (Data Booth), then generate the networking tables on the Tables page.</t>
+          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 31 booths and the 4 breakout classes are already in a fresh database; import the attendee sheet (Data Peserta) and generate the networking tables on the Tables page.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Attendee — any email from the imported sheet; first password = chapter + first name, lowercase without spaces. Booth — booth-&lt;code&gt;@natcon.id / SEED_PASSWORD, created automatically with each booth.</t>
+          <t>Attendee — any email from the imported sheet; first password = chapter + first name, lowercase without spaces. Booth — booth-&lt;code&gt;@natcon.id / SEED_PASSWORD.</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5018,17 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Booths &amp; sponsors</t>
+          <t>Booths</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>import Data Booth.xlsx</t>
+          <t>already there — 31 from the Data Booth sheet</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>each booth gets booth-&lt;code&gt;@natcon.id on SEED_PASSWORD</t>
+          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, e.g. A1 -&gt; booth-a1@natcon.id</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -16,6 +16,7 @@
     <sheet name="06 Reports &amp; export" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="07 Cross-cutting" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="08 Test data" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09 Door crew app" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +66,13 @@
       <b val="1"/>
       <color rgb="00CF2030"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -96,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,6 +128,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -601,7 +613,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 31 booths and the 4 breakout classes are already in a fresh database; import the attendee sheet (Data Peserta) and generate the networking tables on the Tables page.</t>
+          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 34 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; import the attendee sheet (Data Peserta) and generate the networking tables on the Tables page.</t>
         </is>
       </c>
     </row>
@@ -637,6 +649,352 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>The door crew's own app (port 5175 / 8087): class attendance, goodiebags and pins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Pri</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Expected result</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-01</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Open the door app and sign in as door@natcon.id / SEED_PASSWORD.</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>You land on Door Check-in with three modes: Class attendance, Goodiebag, Pin.</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-02</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Try an ATTENDEE email and password.</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Refused with 'That is not a door account. Ask the committee for the door login.' — not a wall of errors on the next screen.</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-03</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Signed out</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Sign in with the wrong password.</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>It says the password is wrong. It must NOT say the session expired.</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-04</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Door app, Class attendance mode</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Pick a class and scan an attendee registered for it.</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Attendance recorded, with their name and chapter. Scanning again says they are already checked in.</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-05</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Door app, Class attendance mode</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Scan an attendee NOT registered for that class.</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Rejected clearly, naming the reason.</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-06</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Door app, Goodiebag mode</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Scan an attendee.</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>'Goodiebag handed over' with their name; the counter moves. The class picker is hidden in this mode.</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-07</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Door app, Goodiebag mode</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Scan the same attendee again.</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>'Already collected — &lt;name&gt; took it at HH:MM'. The time is what settles an argument at the desk.</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-08</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Door app, Pin mode</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Scan an attendee who already has their goodiebag.</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>The pin is handed over: the two are counted separately.</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-09</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Door app</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Type a member code, an email, and a phone number into the manual box.</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>All three find the attendee — a phone that will not scan must not stop the queue.</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>DOOR-10</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Signed in to the door app</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Look for the attendee list, master data, reports or the draws.</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>None of it exists here, and the API refuses a door account those pages. That separation is why this app exists.</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F4:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1363,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1378,7 +1736,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>The attendee app: pass, passport, breakout class, speed networking.</t>
+          <t>The attendee app: pass, passport, learning class, speed networking.</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1964,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Breakout Room tab</t>
+          <t>Learning Class tab</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1756,7 +2114,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Reopen Breakout Room.</t>
+          <t>Reopen Learning Class.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1780,17 +2138,17 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Network tab, not yet at a table</t>
+          <t>Learning class tab, networking</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Type a table number and join.</t>
+          <t>Look for a way to type a table number.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Placement card shows 'Table N · Seat n' and the people already at that table.</t>
+          <t>There is none — scanning the table QR is the only way in. The note says so, and the camera-failure message points at the committee.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -1843,12 +2201,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Type your own member code (NATCON-2026-…) into the table number box.</t>
+          <t>Scan your own member QR at the table screen.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Refused with 'Enter your table number, e.g. 5'. It must NOT seat you at table 1.</t>
+          <t>Refused as 'not a networking table code'. It must NOT seat you at table 1.</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -2051,18 +2409,161 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Logo only — no venue line. The bottom nav reads Home, My QR, Passport, Breakout Room, Network, all on one level.</t>
+          <t>Logo only — no venue line. The bottom nav reads Home, My QR, Passport, Learning Class, Network, all on one level.</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>ATT-23</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Attendee holding one learning class</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Register for a second class at the SAME hour.</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Refused: 'that class runs at the same time as one you already picked'.</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>ATT-24</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Attendee holding one learning class</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Register for a class at a DIFFERENT hour.</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Accepted — two classes is the allowance.</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>ATT-25</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Attendee holding two learning classes</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Register for a third.</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Refused: two is the limit. Cancelling one frees the place immediately.</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ATT-26</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Two attendees seated at the same table</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Have the second one scan in while the first watches.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>The newcomer appears on the first one's screen within about five seconds, with Save and Note ready — no refresh.</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>ATT-27</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Attendee whose email holds two tickets</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Sign in.</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>The picker numbers the passes #1 and #2 above their member codes, so two identical names can be told apart.</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F4:F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2071,1485 +2572,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>The booth/sponsor app used at the stand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Pri</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Expected result</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>BTH-01</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Signed in as a booth on a phone</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Open Scanner and allow the camera.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Live camera preview appears.</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>BTH-02</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Camera on</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Scan an attendee's QR from their My QR screen.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>'Scan successful' with their name, chapter, and 'pin +1 (total N)'.</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>BTH-03</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Camera blocked or unavailable</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Open Scanner.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>A clear message says the camera is unavailable and points to the manual input below — the page still works.</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>BTH-04</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Scanner</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Type an attendee's member code into manual input and submit.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Same successful result as a camera scan.</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>BTH-05</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Scanner</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Type the attendee's PHONE number instead of the member code.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Resolves to the same person.</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>BTH-06</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>The same attendee was already scanned at this booth</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Scan or type them again.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>'Already scanned' — says the pin count is unchanged. It must not add a second pin.</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>BTH-07</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Scanner</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Type a code that belongs to nobody, e.g. NATCON-2026-99999.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>A clear not-found message. Nothing is recorded.</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>BTH-08</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Scanner</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Type a booth QR payload (BOOTH:A1) into manual input.</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Refused — it is not an attendee code.</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>BTH-09</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>At least one scan today</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Open Dashboard.</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Total scans and Scans today match what you scanned; the visitor appears in Recent visitors.</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>BTH-10</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Tap a visitor row.</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Visitor detail: name, company, chapter, member code, visit time, a Call button, and a Lead note box.</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>BTH-11</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Visitor detail</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Write a lead note, save, then go back to the dashboard.</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>The note is shown on that visitor's row in the list straight away — without reloading the page.</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>BTH-12</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Signed in as a sponsor booth (booth-sp01@natcon.id)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Repeat BTH-04.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Works the same; sponsors scan exactly like booths.</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>BTH-13</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Phone with the app open</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Turn off mobile data and Wi-Fi, then scan an attendee.</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Shows 'Offline — scan queued'. Turn the connection back on: the queued scan syncs and the attendee's pin appears.</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>BTH-14</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Booth app</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Look at the bottom nav.</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Only Scanner and Dashboard — no attendee tabs.</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F4:F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Attendees, tenants, breakout classes, chapters — CRUD and Excel import.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Pri</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Expected result</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>MD-01</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Admin, Attendees page</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Look at the list.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Paginated table with the total count. Each row shows name, email, member code, chapter, company, phone and pin count.</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>MD-02</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Attendees page</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Type part of a name, an email, or a phone into search.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>The list narrows to matching rows and the total updates.</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>MD-03</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Attendees page</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Press + Add Attendee, fill name, email, chapter, phone. Save.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>The attendee appears with a generated member code NATCON-2026-….</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>MD-04</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Continuing MD-03</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Open that attendee's Detail.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Profile with chapter, company, phone, classification, plus their visits and class registrations.</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>MD-05</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Attendees page</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Edit an attendee, change the chapter, save. Reopen the row.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>The change stuck; nothing else on the row was blanked.</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>MD-06</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Attendees page</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Press Download format, then import that same file back.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Imports without errors — the template must be importable by its own importer.</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>MD-07</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>The official ticketing export (Data Peserta .xlsx)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Press Import Excel and choose it.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Reports created / updated / failed. Attendees appear with chapter, company, classification and normalized phones (+62…).</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>MD-08</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>After MD-07</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Import the SAME file a second time.</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Everything is reported as updated, not created — no duplicates.</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>MD-09</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>A sheet where one email holds two ticket numbers</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Import it.</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Both rows import as two separate attendees on the same email.</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>MD-10</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Tenants page</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Look at the list.</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Filter tabs All / Sponsors / Booths with live counts, a Kind column, and sponsor rows tinted.</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>MD-11</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Tenants page</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Press Download format, then Import Excel with the official Data Booth sheet.</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Booths import: Company Name becomes the booth, Business Classification the category, and Name + BNI Chapter become the booth contact.</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>MD-12</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>After MD-11</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Open a booth's Detail.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Shows kind, booth code, category, booth contact, BNI chapter and the scanner login (booth-&lt;code&gt;@natcon.id).</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>MD-13</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Tenants page</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Edit a booth, change only the category, save, then reopen Edit.</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>The description and contact are still there — editing must not blank the fields it did not touch.</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>MD-14</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Tenants page</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Add a tenant with Kind = Sponsor.</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>It appears under Sponsors, the count goes up, and it shows above booths on the attendee passport.</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>MD-15</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Breakout Classes page</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Press Edit on a class.</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Slot, room, title, speakers, moderator, capacity, description, the speaker list with photos, and the cover are all filled in — nothing blank.</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>MD-16</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Class edit modal</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Add a person, set the role to Moderator, upload a photo, save. Reopen.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>The person and photo persisted and appear on the attendee class card.</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>MD-17</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Class edit modal</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Upload a cover image and save.</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>The cover shows on the attendee class card and detail.</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>MD-18</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Class detail page</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Register an attendee by member code, then by email, then by phone.</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Each is added to the attendee list of that class.</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>MD-19</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Class detail</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Register the same attendee twice.</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Reported as already registered — not added twice.</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>MD-20</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Class detail</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Register an attendee who is already in a DIFFERENT class in the same slot.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Refused, saying they already hold another class in that slot.</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>MD-21</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Class detail</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Press Remove on a registered attendee.</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>They disappear from the list and the seat is freed.</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>MD-22</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Breakout Classes page</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Press Download format, fill a couple of rows (attendee + room), then Import Registrations.</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Reports created / updated / failed; the attendees show on the class detail.</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>MD-23</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Chapters page</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Look at the list; add a chapter, rename one used by attendees.</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Chapters list with member counts. A rename cascades to the attendees in that chapter.</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>MD-24</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Any master-data page</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Import a file with a bad row (no email, or a malformed email).</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>The good rows still import; the bad row is reported with its row number and reason.</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>MD-25</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Admin · Breakout Classes</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Read the Quota column for a class nobody has registered for.</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>Shows taken/quota (e.g. 0/60), an empty fill bar and 'N seats left'.</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>MD-26</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Admin · Breakout Classes</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Click the quota number, type 45, press Enter.</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Saves without opening the edit form; the row shows 0/45 and '45 seats left'. Re-open the class in Edit: description, cover and speaker photos are untouched.</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>MD-27</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Admin · Breakout Classes</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Click the quota number, change it, press Esc.</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>The editor closes and the old quota stays — nothing was saved.</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>MD-28</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>A class with 3 attendees registered</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Set its quota to 2.</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Refused, with '3 already registered — cancel registrations first'. The old quota is still in place after a page reload.</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>MD-29</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Same class, 3 registered</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Set its quota to exactly 3.</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Accepted. The row reads 3/3 with a full bar and FULL in red.</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>MD-30</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>A class showing FULL</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Register one more attendee into it (Detail → register by code/email/phone).</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>Refused: 'this seminar is fully booked'. An attendee picking it in the app is turned away too.</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>MD-31</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Admin · Breakout Classes</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Open Edit on a class with registrations and set Quota below that count.</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>The full edit form refuses it exactly like the quota cell does.</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>MD-32</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Admin · Breakout Classes</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Set a quota of 0 or a negative number.</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Refused — the quota must be at least 1.</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="F4:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3570,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Door check-in, tables, QR prints, lucky draw, dashboard.</t>
+          <t>The booth/sponsor app used at the stand.</t>
         </is>
       </c>
     </row>
@@ -3614,7 +2636,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>BTH-01</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -3624,17 +2646,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Admin, Dashboard</t>
+          <t>Signed in as a booth on a phone</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Look at the tiles.</t>
+          <t>Open Scanner and allow the camera.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Registered attendees, Sponsors and Booths counted separately, total visit scans, scans today, class registrations.</t>
+          <t>Live camera preview appears.</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
@@ -3643,27 +2665,27 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>OPS-02</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>BTH-02</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Camera on</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Leave it open while a booth records a scan.</t>
+          <t>Scan an attendee's QR from their My QR screen.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Within a few seconds the scan count and the activity feed update on their own.</t>
+          <t>'Scan successful' with their name, chapter, and 'pin +1 (total N)'.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
@@ -3672,7 +2694,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>OPS-03</t>
+          <t>BTH-03</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -3682,17 +2704,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Door Check-in</t>
+          <t>Camera blocked or unavailable</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Pick a breakout room from the dropdown.</t>
+          <t>Open Scanner.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Shows attended / registered / percentage for that room.</t>
+          <t>A clear message says the camera is unavailable and points to the manual input below — the page still works.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
@@ -3701,7 +2723,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>BTH-04</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -3711,17 +2733,17 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Door Check-in, an attendee registered for that room</t>
+          <t>Scanner</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Type their member code and check in.</t>
+          <t>Type an attendee's member code into manual input and submit.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>'Attendance recorded' with their name; attended count goes up by one.</t>
+          <t>Same successful result as a camera scan.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
@@ -3730,7 +2752,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>OPS-05</t>
+          <t>BTH-05</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -3740,17 +2762,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Continuing OPS-04</t>
+          <t>Scanner</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Check the same person in again.</t>
+          <t>Type the attendee's PHONE number instead of the member code.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>'Already checked in' — the count does not move.</t>
+          <t>Resolves to the same person.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
@@ -3759,7 +2781,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>OPS-06</t>
+          <t>BTH-06</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -3769,17 +2791,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Door Check-in on the WRONG room</t>
+          <t>The same attendee was already scanned at this booth</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Check in someone registered elsewhere.</t>
+          <t>Scan or type them again.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Rejected: not registered for this class. Nothing recorded.</t>
+          <t>'Already scanned' — says the pin count is unchanged. It must not add a second pin.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -3788,27 +2810,27 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>OPS-07</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>BTH-07</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Door Check-in on a phone</t>
+          <t>Scanner</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Scan a printed room QR (SEMINAR:&lt;id&gt;).</t>
+          <t>Type a code that belongs to nobody, e.g. NATCON-2026-99999.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>The page switches to that room instead of treating it as an attendee.</t>
+          <t>A clear not-found message. Nothing is recorded.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
@@ -3817,7 +2839,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>OPS-08</t>
+          <t>BTH-08</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -3827,17 +2849,17 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Door Check-in with a camera</t>
+          <t>Scanner</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Scan an attendee's QR.</t>
+          <t>Type a booth QR payload (BOOTH:A1) into manual input.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Same result as typing the code.</t>
+          <t>Refused — it is not an attendee code.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -3846,7 +2868,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>OPS-09</t>
+          <t>BTH-09</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -3856,17 +2878,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Tables page</t>
+          <t>At least one scan today</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Generate tables: choose how many and seats per table.</t>
+          <t>Open Dashboard.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>The tables are created and listed; the attendee app can join them by number.</t>
+          <t>Total scans and Scans today match what you scanned; the visitor appears in Recent visitors.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
@@ -3875,27 +2897,27 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>OPS-10</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>BTH-10</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Tables page</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Delete a table nobody is sitting at.</t>
+          <t>Tap a visitor row.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>It disappears from the list and from the attendee app.</t>
+          <t>Visitor detail: name, company, chapter, member code, visit time, a Call button, and a Lead note box.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -3904,7 +2926,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>OPS-11</t>
+          <t>BTH-11</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -3914,17 +2936,17 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>QR Prints</t>
+          <t>Visitor detail</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Open the page and pick a size.</t>
+          <t>Write a lead note, save, then go back to the dashboard.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Print-ready QR cards for tables, class rooms and booth signage, each labelled.</t>
+          <t>The note is shown on that visitor's row in the list straight away — without reloading the page.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
@@ -3933,27 +2955,27 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>OPS-12</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>BTH-12</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>QR Prints</t>
+          <t>Signed in as a sponsor booth (booth-b1@natcon.id)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Print (or print-preview) a page of table QRs, then scan one with the attendee app.</t>
+          <t>Repeat BTH-04.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>The scanned QR joins exactly that table — the printed number matches.</t>
+          <t>Works the same; sponsors scan exactly like booths.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
@@ -3962,27 +2984,27 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>OPS-13</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>BTH-13</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Lucky Draw, attendee list imported</t>
+          <t>Phone with the app open</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Open the page.</t>
+          <t>Turn off mobile data and Wi-Fi, then scan an attendee.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Shows the eligible count. It must equal the TOTAL number of registered attendees — pins do not decide eligibility. Check against Master Data → Attendees.</t>
+          <t>Shows 'Offline — scan queued'. Turn the connection back on: the queued scan syncs and the attendee's pin appears.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -3991,94 +3013,92 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>OPS-14</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>BTH-14</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Lucky Draw</t>
+          <t>Booth app</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Press Shuffle &amp; draw a winner.</t>
+          <t>Look at the bottom nav.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Cards shuffle and one winner is shown with their name and chapter.</t>
+          <t>Only Scanner and Dashboard — no attendee tabs.</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>OPS-15</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>BTH-15</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Scanner, an attendee holding a ticket from the sheet</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Scan their pass QR from the My QR screen.</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Recorded, with their name — the QR carries the ticket number, not the member code.</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>BTH-16</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>After OPS-14</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Draw again.</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>The previous winner is not drawn a second time.</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>OPS-16</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Delete an attendee who has scans and a class registration.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Deleted after the confirmation, and their scans and registration go with them; counts on the dashboard drop accordingly.</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Scanner, the same attendee</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Type the member code printed under their QR instead.</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Reported as a repeat visit of the same person — both keys reach one attendee, never two.</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>OPS-24</t>
+          <t>BTH-17</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -4088,17 +3108,17 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Lucky Draw</t>
+          <t>Scanner</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Press Stage mode, then Space, then Esc.</t>
+          <t>Type a ticket number nobody holds (16C6C-NOSUCHTICKET).</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Space draws one winner (never two, however fast you press). Esc returns to the panel and the page is where you left it.</t>
+          <t>A clear not-found message. Nothing is recorded.</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr"/>
@@ -4107,8 +3127,2285 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="F4:F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Attendees, tenants, learning classes, chapters — CRUD and Excel import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Pri</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Expected result</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>MD-01</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Admin, Attendees page</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Look at the list.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Paginated table with the total count. Each row shows name, email, member code, chapter, company, phone and pin count.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>MD-02</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Attendees page</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type part of a name, an email, or a phone into search.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>The list narrows to matching rows and the total updates.</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>MD-03</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Attendees page</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Press + Add Attendee, fill name, email, chapter, phone. Save.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>The attendee appears with a generated member code NATCON-2026-….</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>MD-04</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Continuing MD-03</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Open that attendee's Detail.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Profile with chapter, company, phone, classification, plus their visits and class registrations.</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>MD-05</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Attendees page</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Edit an attendee, change the chapter, save. Reopen the row.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>The change stuck; nothing else on the row was blanked.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>MD-06</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Attendees page</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Press Download format, then import that same file back.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Imports without errors — the template must be importable by its own importer.</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>MD-07</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>The official ticketing export (Data Peserta .xlsx)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Press Import Excel and choose it.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Reports created / updated / failed. Attendees appear with chapter, company, classification and normalized phones (+62…).</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>MD-08</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>After MD-07</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Import the SAME file a second time.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Everything is reported as updated, not created — no duplicates.</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MD-09</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>A sheet where one email holds two ticket numbers</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Import it.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Both rows import as two separate attendees on the same email.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>MD-10</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Tenants page</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Look at the list.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Filter tabs All / Sponsors / Booths with live counts, a Kind column, and sponsor rows tinted.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>MD-11</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Tenants page</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Press Download format, then Import Excel with the official Data Booth sheet.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Booths import: Company Name becomes the booth, Business Classification the category, and Name + BNI Chapter become the booth contact.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>MD-12</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>After MD-11</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Open a booth's Detail.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Shows kind, booth code, category, booth contact, BNI chapter and the scanner login (booth-&lt;code&gt;@natcon.id).</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>MD-13</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Tenants page</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Edit a booth, change only the category, save, then reopen Edit.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>The description and contact are still there — editing must not blank the fields it did not touch.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>MD-14</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Tenants page</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Add a tenant with Kind = Sponsor.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>It appears under Sponsors, the count goes up, and it shows above booths on the attendee passport.</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>MD-15</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Learning Classes page</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Press Edit on a class.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Slot, room, title, speakers, moderator, capacity, description, the speaker list with photos, and the cover are all filled in — nothing blank.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>MD-16</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Class edit modal</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Add a person, set the role to Moderator, upload a photo, save. Reopen.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>The person and photo persisted and appear on the attendee class card.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>MD-17</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Class edit modal</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Upload a cover image and save.</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>The cover shows on the attendee class card and detail.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>MD-18</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Class detail page</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Register an attendee by member code, then by email, then by phone.</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Each is added to the attendee list of that class.</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>MD-19</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Class detail</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Register the same attendee twice.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Reported as already registered — not added twice.</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>MD-20</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Class detail</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Register an attendee who is already in a DIFFERENT class in the same slot.</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Refused, saying they already hold another class in that slot.</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>MD-21</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Class detail</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Press Remove on a registered attendee.</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>They disappear from the list and the seat is freed.</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>MD-22</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Learning Classes page</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Press Download format, fill a couple of rows (attendee + room), then Import Registrations.</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Reports created / updated / failed; the attendees show on the class detail.</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>MD-23</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Chapters page</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Look at the list; add a chapter, rename one used by attendees.</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Chapters list with member counts. A rename cascades to the attendees in that chapter.</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>MD-24</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Any master-data page</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Import a file with a bad row (no email, or a malformed email).</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>The good rows still import; the bad row is reported with its row number and reason.</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>MD-25</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Learning Classes</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Read the Quota column for a class nobody has registered for.</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Shows taken/quota (e.g. 0/60), an empty fill bar and 'N seats left'.</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>MD-26</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Learning Classes</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Click the quota number, type 45, press Enter.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Saves without opening the edit form; the row shows 0/45 and '45 seats left'. Re-open the class in Edit: description, cover and speaker photos are untouched.</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>MD-27</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Learning Classes</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Click the quota number, change it, press Esc.</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>The editor closes and the old quota stays — nothing was saved.</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>MD-28</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>A class with 3 attendees registered</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Set its quota to 2.</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Refused, with '3 already registered — cancel registrations first'. The old quota is still in place after a page reload.</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>MD-29</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Same class, 3 registered</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Set its quota to exactly 3.</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Accepted. The row reads 3/3 with a full bar and FULL in red.</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>MD-30</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>A class showing FULL</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Register one more attendee into it (Detail → register by code/email/phone).</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Refused: 'this seminar is fully booked'. An attendee picking it in the app is turned away too.</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>MD-31</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Learning Classes</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Open Edit on a class with registrations and set Quota below that count.</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>The full edit form refuses it exactly like the quota cell does.</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>MD-32</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Learning Classes</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Set a quota of 0 or a negative number.</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Refused — the quota must be at least 1.</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>MD-33</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Learning Classes, rundown has learning blocks</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Edit a class and pick a Time block.</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>The list shows the class's hour instead of 'not scheduled'; the attendee's class card shows the same hour.</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>MD-34</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Learning Classes</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Upload a landscape Banner image and a portrait Poster on the same class.</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>The class list shows the banner; the attendee's class detail shows the poster whole, not cropped.</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>MD-35</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>A class with both pictures</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Edit only its description and save.</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Both pictures survive. Losing one on an unrelated save is the bug this case exists for.</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>MD-36</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tenants</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Upload a Company logo on a booth.</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>The attendee passport shows the logo in place of the two-letter initials; booths without a logo still show initials.</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>MD-37</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Attendees imported from a sheet where several share a name, email and phone</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Search for that email in Master Data → Attendees.</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Each row carries #1 of 3, #2 of 3 … so identical-looking rows can be told apart.</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>MD-38</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Attendees</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Add an attendee by hand and give them a Ticket number.</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Saved and shown under their member code in the list; their pass QR then carries that number.</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>MD-39</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Attendees</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Give a second attendee a ticket number another one already holds.</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Refused — 'that ticket number belongs to another attendee'. Two people on one QR is the thing this prevents.</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>MD-40</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>An attendee imported with a ticket number</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Edit only their phone number and save.</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>The ticket number is still there. Losing it would make their QR stop scanning.</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="F4:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Door check-in, tables, QR prints, lucky draw, dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Pri</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Expected result</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Admin, Dashboard</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Look at the tiles.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Registered attendees, Sponsors and Booths counted separately, total visit scans, scans today, class registrations.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>OPS-02</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Leave it open while a booth records a scan.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Within a few seconds the scan count and the activity feed update on their own.</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>OPS-03</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Door Check-in</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Pick a learning class from the dropdown.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Shows attended / registered / percentage for that room.</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>OPS-04</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Door Check-in, an attendee registered for that room</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Type their member code and check in.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>'Attendance recorded' with their name; attended count goes up by one.</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>OPS-05</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Continuing OPS-04</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Check the same person in again.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>'Already checked in' — the count does not move.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>OPS-06</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Door Check-in on the WRONG room</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Check in someone registered elsewhere.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Rejected: not registered for this class. Nothing recorded.</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>OPS-07</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Door Check-in on a phone</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Scan a printed room QR (SEMINAR:&lt;id&gt;).</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>The page switches to that room instead of treating it as an attendee.</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>OPS-08</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Door Check-in with a camera</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Scan an attendee's QR.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Same result as typing the code.</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>OPS-09</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Tables page</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Generate tables: choose how many and seats per table.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>The tables are created and listed; the attendee app can join them by number.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>OPS-10</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Tables page</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Delete a table nobody is sitting at.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>It disappears from the list and from the attendee app.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>OPS-11</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>QR Prints</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Open the page and pick a size.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Print-ready QR cards for tables, class rooms and booth signage, each labelled.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>OPS-12</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>QR Prints</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Print (or print-preview) a page of table QRs, then scan one with the attendee app.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>The scanned QR joins exactly that table — the printed number matches.</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>OPS-13</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Lucky Draw, attendee list imported</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Open the page.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Shows the eligible count. It must equal the TOTAL number of registered attendees — pins do not decide eligibility. Check against Master Data → Attendees.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>OPS-14</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Lucky Draw</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Press Shuffle &amp; draw a winner.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Cards shuffle and one winner is shown with their name and chapter.</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>OPS-15</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>After OPS-14</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Draw again.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>The previous winner is not drawn a second time.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>OPS-16</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Delete an attendee who has scans and a class registration.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Deleted after the confirmation, and their scans and registration go with them; counts on the dashboard drop accordingly.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>OPS-24</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Lucky Draw</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Press Stage mode, then Space, then Esc.</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Space draws one winner (never two, however fast you press). Esc returns to the panel and the page is where you left it.</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>OPS-25</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown, empty</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Add a block: 09:00, 1 hour, Plenary, 'Opening Ceremony', Grand Ballroom.</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>It appears in the table as 09:00 – 10:00 · 1 hour · Plenary. The attendee app's Today's agenda shows it without a redeploy.</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>OPS-26</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Try to add a block starting at 13:30, and one that is 90 minutes long.</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Both refused: blocks start on the hour and run in whole hours.</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>OPS-27</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown with two blocks at the same time</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Look at the table.</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Both overlapping rows are tinted and marked 'overlaps another block'.</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>OPS-28</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Delete a block that has a learning class in it.</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>The block goes, the class stays — it simply has no time until you give it a new block.</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>OPS-29</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tables, nobody seated</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Press Start round with 15 minutes.</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>The panel reads 'Round 1 is running · ends at HH:MM'. Every attendee's Network screen counts down to that same time.</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>OPS-30</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>A round is running, attendee on the Network screen</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Reload the attendee's page.</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>The countdown continues from where it was. It must NOT restart at 15:00 — that was the old bug.</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>OPS-31</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>A round is running</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Press Start next round.</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>The old round closes and a new one starts. Attendees follow within about 20 seconds; there are never two clocks.</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>OPS-32</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>No round has ever started</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Look at an attendee's Network screen.</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>The clock reads --:-- and 'waiting to start', not an invented number.</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>OPS-33</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tables, some attendees seated</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Press 'Who is seated'.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Each table lists who is sitting at it with chapter, company and the time they sat down. The header count agrees with the list.</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>OPS-34</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tables, seating on screen</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Press Export Excel.</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>natcon2026-networking-seating.xlsx downloads with table, seat, member code, name, chapter, company, phone and joined-at.</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>OPS-35</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tables</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Edit table 1 and give it the name 'Startup Corner'.</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>The list shows the name; an attendee seated there sees 'Startup Corner' on their placement card.</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>OPS-36</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Lucky Draw</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Look at the top of the page.</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Two tabs: Lucky Draw and Doorprize, each showing how many have been drawn.</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>OPS-37</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Lucky Draw</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Set 'Booths to visit before entering' to 5.</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>The eligible count drops to only those who have visited five or more booths. Setting it back to 0 restores everyone.</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>OPS-38</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Lucky Draw</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Draw a winner, then RELOAD the page.</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>The winner is still listed and still out of the pool. Losing them on reload was the old behaviour and must not come back.</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>OPS-39</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>A lucky draw winner exists</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Switch to the Doorprize tab.</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>It has its own (empty) winners list, and the lucky draw's winner is not in its pool — nobody takes two prizes.</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>OPS-40</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Admin · a draw whose pool is empty</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Press draw.</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Refused with 'nobody left to draw — everyone eligible has already won', not a silent failure.</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>OPS-41</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Lucky Draw with winners</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Press Clear winners and confirm.</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>The list empties and everyone returns to the pool — for a rehearsal, or a ceremony that restarts.</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="2">
     <dataValidation sqref="F4:F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,Blocked,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4481,7 +5778,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Breakout Classes page</t>
+          <t>Learning Classes page</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -4619,7 +5916,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Walk the attendee app: Home, My QR, Passport, Breakout Room, Network.</t>
+          <t>Walk the attendee app: Home, My QR, Passport, Learning Class, Network.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -4939,7 +6236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5023,12 +6320,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>already there — 31 from the Data Booth sheet</t>
+          <t>already there — 34 booths + 4 sponsors from the booth sheet</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, e.g. A1 -&gt; booth-a1@natcon.id</t>
+          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, e.g. A1 -&gt; booth-a1@natcon.id. A18/A20 and A47/A48 are one company on two stands.</t>
         </is>
       </c>
     </row>
@@ -5057,12 +6354,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>booth-sp01@natcon.id / natcon2026</t>
+          <t>booth-b1@natcon.id / SEED_PASSWORD</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>BNI Xpora · booth SP-01</t>
+          <t>Bio Medika · booth B1 — the sheet's own Sponsor divider made it a sponsor</t>
         </is>
       </c>
     </row>
@@ -5171,17 +6468,17 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Breakout classes</t>
+          <t>Learning classes</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Rooms 1–4, all slot 1, 60 seats each</t>
+          <t>Rooms 1–4, 60 seats each</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>All parallel — an attendee picks exactly one</t>
+          <t>Give each one a rundown block before testing the two-class rule</t>
         </is>
       </c>
     </row>
@@ -5242,6 +6539,40 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>The door given to booth and sponsor crews</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Attendee QR payload</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>their ticket number, e.g. 16C6C-23BBA1745</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>What the pass QR carries. The member code under it still scans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Unknown ticket number</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>16C6C-NOSUCHTICKET</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>For the not-found cases at any scanner</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -4373,7 +4373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4934,17 +4934,17 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Admin · Rundown, empty</t>
+          <t>Admin · Rundown, fresh database</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Add a block: 09:00, 1 hour, Plenary, 'Opening Ceremony', Grand Ballroom.</t>
+          <t>Open the page before touching anything, then add a block: 09:00, 1 hour, Plenary, 'Opening Ceremony', Grand Ballroom.</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>It appears in the table as 09:00 – 10:00 · 1 hour · Plenary. The attendee app's Today's agenda shows it without a redeploy.</t>
+          <t>The day already carries nine draft blocks, registration first and the draw last, two of them Learning Class. The new block appears as 09:00 – 10:00 · 1 hour · Plenary, and the attendee app's agenda shows it without a redeploy.</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr"/>
@@ -5396,6 +5396,62 @@
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>OPS-42</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown, draft blocks untouched</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Delete a draft block, then restart the API (or ask for a redeploy).</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>It stays deleted. The draft is only ever written into an empty schedule.</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>OPS-43</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown with two learning blocks</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Put two classes in the 13:00 block and two in the 14:00 block, from the Learning Classes page.</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Each class shows its hour. An attendee can then hold one from each block, but never two from the same one.</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6236,7 +6292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6576,6 +6632,23 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Rundown</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>9 draft blocks on 3 Sep, 07:00 → 18:00</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Seeded only when the schedule is empty; two of them are Learning Class blocks</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2554,6 +2554,34 @@
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>ATT-28</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Attendee home screen, rundown covering both days</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Read the agenda card top to bottom.</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>It is headed 'Agenda', 3 September first, then a 'Friday 4 September' heading before the Gold Club Breakfast — which says on it that it is for Gold Club tickets.</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4373,7 +4401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4944,7 +4972,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>The day already carries nine draft blocks, registration first and the draw last, two of them Learning Class. The new block appears as 09:00 – 10:00 · 1 hour · Plenary, and the attendee app's agenda shows it without a redeploy.</t>
+          <t>The day already carries ten draft blocks — nine on 3 September, registration first and the draw last, two of them Learning Class, plus the Gold Club Breakfast under its own 'Friday 4 September' heading. The new block appears as 09:00 – 10:00 · 1 hour · Plenary, and the attendee agenda shows it without a redeploy.</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr"/>
@@ -5452,6 +5480,62 @@
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>OPS-44</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Add a block and pick 'Friday 4 September' in the Day field.</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>It lands under the 4 September heading, below every 3 September block — not mixed into the conference day.</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>OPS-45</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Rundown, two days on screen</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Compare a 3 September block with a 4 September block at the same hour.</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>Neither is flagged as overlapping. Same hour on different days is not a clash.</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6640,7 +6724,7 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>9 draft blocks on 3 Sep, 07:00 → 18:00</t>
+          <t>10 draft blocks: 9 on 3 Sep (07:00 → 18:00) + Gold Club Breakfast 4 Sep 08:00–11:00</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2582,6 +2582,34 @@
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>ATT-29</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Attendee passport</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Scroll the booth list.</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>The exhibitors who sent a logo show it; the rest show their two-letter initials. No empty grey squares.</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3173,7 +3201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4372,6 +4400,62 @@
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>MD-41</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tenants, a booth with no logo</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>Edit it, change only the description, save. Then open the attendee passport.</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>Its initials are still on the tile. A save that leaves the initials field alone must not empty it.</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>MD-42</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tenants, a booth whose logo shipped with the app</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Upload a different logo, then ask for a restart/redeploy.</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>The uploaded one stays. The shipped logo only fills a booth that has none.</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5982,7 +6066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6201,12 +6285,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Turn on Demo (Mock) mode and sign in with any password.</t>
+          <t>Look for a Demo / Mock mode switch.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>The app runs on local demo data with a red DEMO chip. No backend needed.</t>
+          <t>There is none — it was removed so nobody demos fake data at the venue by accident.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -6225,17 +6309,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Demo mode</t>
+          <t>An attendee whose email holds two tickets</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Sign in as duo@natcon.id.</t>
+          <t>Sign in with that email.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>The 'Which one are you?' chooser appears — two tickets on one email.</t>
+          <t>The 'Which one are you?' chooser appears, numbering the passes #1 and #2.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
@@ -6356,6 +6440,90 @@
       </c>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>CRS-12</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>The door or admin password, typed into the ATTENDEE sign-in</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Sign in as door@natcon.id at /login.</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>A card says it is a door crew account, links to the door app, and offers Sign out. It must NOT be a blank page — that was the bug: the app bounced the account between /attendee and itself forever.</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>CRS-13</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Any attendee screen</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Ask the developer to force a render error.</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>A card says the screen stopped working, with Reload and Sign out. Never a white page.</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>CRS-14</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Attendee app open on a phone, then a new version is deployed</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Close and reopen the app (or reload twice).</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>It comes up on the new version. The cache is per build, so a deploy cannot leave a phone on the old one — or worse, on a shell whose files the deploy deleted.</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 34 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; import the attendee sheet (Data Peserta) and generate the networking tables on the Tables page.</t>
+          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 32 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; import the attendee sheet (Data Peserta) and generate the networking tables on the Tables page.</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2610,6 +2610,34 @@
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ATT-30</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Attendee scanned at both stands of a double-width booth</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Open the passport and count the stamps.</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>That company gives one stamp and appears once. Two stands are one exhibitor, so it counts once towards the lucky draw's booth minimum too.</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3201,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4456,6 +4484,34 @@
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>MD-43</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tenants</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>Find GrasiaCare and Alpha leaders in the list.</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>One row each, booth reading 'A18 &amp; A20' and 'A47 &amp; A48'. Not two rows — one company on two stands is one exhibitor, with one login and one QR to print for both signs.</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6628,12 +6684,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>already there — 34 booths + 4 sponsors from the booth sheet</t>
+          <t>already there — 32 booths + 4 sponsors from the booth sheet</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, e.g. A1 -&gt; booth-a1@natcon.id. A18/A20 and A47/A48 are one company on two stands.</t>
+          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, e.g. A1 -&gt; booth-a1@natcon.id. A brand on two stands is ONE booth labelled 'A18 &amp; A20', logging in as booth-a18@natcon.id.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -3229,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4512,6 +4512,34 @@
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>MD-44</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Admin · Tenants, some booths have a logo</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Look down the Name column, then open the Dashboard's Booth Ranking and one booth's detail page.</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>A booth with a logo shows it in all three; the rest show their two letters. That is how you spot which companies still owe the committee a logo.</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -3229,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Find GrasiaCare and Alpha leaders in the list.</t>
+          <t>Find Alpha leaders in the list, then check GrasiaCare and Paper.id.</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>One row each, booth reading 'A18 &amp; A20' and 'A47 &amp; A48'. Not two rows — one company on two stands is one exhibitor, with one login and one QR to print for both signs.</t>
+          <t>Alpha leaders is one row reading 'A47 &amp; A48' — one company on two stands is one exhibitor, with one login and one QR for both signs. GrasiaCare sits on A18 alone and Paper.id on A20: the floor plan follows the committee's latest numbering, not the older sheet.</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
@@ -4536,10 +4536,38 @@
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>A booth with a logo shows it in all three; the rest show their two letters. That is how you spot which companies still owe the committee a logo.</t>
+          <t>Every exhibitor except Bio Medika and ProSnap shows their own logo in all three; those two show their initials. That is how you spot who still owes the committee a logo.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>MD-45</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Admin · QR Prints, after a floor-plan update</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Print the booth QRs and compare a few against the signs on the floor.</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>Every code matches the stand it is standing on. Old prints from before the renumbering are wrong and must be thrown away — the codes moved.</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6717,7 +6745,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, e.g. A1 -&gt; booth-a1@natcon.id. A brand on two stands is ONE booth labelled 'A18 &amp; A20', logging in as booth-a18@natcon.id.</t>
+          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, following the stand — Paper.id is on A20, so booth-a20@natcon.id. Alpha leaders holds two stands as one booth, 'A47 &amp; A48', logging in as booth-a47@natcon.id.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -6178,7 +6178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6636,6 +6636,62 @@
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>CRS-15</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>A phone (or a 375px window)</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Open all four sign-ins: /login, /tenant/login, the admin panel, the door app.</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Each one is a single column — brand on top, form below it at full width, fields and the Sign in button big enough to tap. Nothing scrolls sideways and the brand appears once, not twice.</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>CRS-16</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>The door app on a phone</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Look at the sign-in fields and the Show button.</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>They are styled like the other apps — rounded fields with an icon, a Show/Hide toggle on the password. Plain browser boxes mean the stylesheet is not matching the markup.</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -727,12 +727,12 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Open the door app and sign in as door@natcon.id / SEED_PASSWORD.</t>
+          <t>Open /door/login and sign in as door@natcon.id / SEED_PASSWORD.</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>You land on Door Check-in with three modes: Class attendance, Goodiebag, Pin.</t>
+          <t>You land on Door Check-in with three modes: Class attendance, Goodiebag, Pin — and the address becomes /door.</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr"/>
@@ -6712,7 +6712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7069,6 +7069,23 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Door crew app</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>/door/login</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Its own path, like /login and /tenant/login. The bare address redirects there.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 32 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; import the attendee sheet (Data Peserta) and generate the networking tables on the Tables page.</t>
+          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 32 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; the 769 attendees are seeded too (Data Peserta) and generate the networking tables on the Tables page.</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>import Data Peserta.xlsx</t>
+          <t>already there — 769 from the ticketing export</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>769 rows; password = chapter + first name, then they set their own</t>
+          <t>Seeded by migration 0028. Password = chapter + first name, lowercase, no spaces; they must change it on first sign-in.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2638,6 +2638,34 @@
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>ATT-31</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Attendee · Learning Class tab</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Look at the four class cards.</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Each carries the committee's banner with its own speakers on it — not a plain gradient, and not the same picture on two classes.</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2666,6 +2666,62 @@
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>ATT-32</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>An attendee signing in for the very first time</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Watch what happens after the password screen.</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>A six-step tour opens by itself, explaining the pass, the QR, the passport, the classes and networking — each step on top of the screen it is describing.</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>ATT-33</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>An attendee who has already seen the tour</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Sign in again, then press 'How to use this app' on Home.</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>It does not open by itself a second time, and the button starts it again from step 1. Back, Next and Skip all work, and Skip counts as seen.</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2722,6 +2722,34 @@
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>ATT-34</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>The tour open on a phone with the volume up</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Listen, then press the speaker button.</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Each step is read out loud; the speaker button silences it, stops what is being said mid-sentence, and it stays silent the next time the tour is opened.</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -2713,12 +2713,12 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Sign in again, then press 'How to use this app' on Home.</t>
+          <t>Sign in again, then press 'Quick tour' in the top bar — try it from the Passport screen, not Home.</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>It does not open by itself a second time, and the button starts it again from step 1. Back, Next and Skip all work, and Skip counts as seen.</t>
+          <t>It does not open by itself a second time. The button is beside Log out on every attendee screen, and starting it from anywhere returns to step 1 on Home. Back, Next and Skip all work, and Skip counts as seen.</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -2685,12 +2685,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Watch what happens after the password screen.</t>
+          <t>Sign in and watch the Home screen, then press 'Quick tour' in the top bar.</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>A six-step tour opens by itself, explaining the pass, the QR, the passport, the classes and networking — each step on top of the screen it is describing.</t>
+          <t>Nothing opens by itself. Pressing the button starts a six-step tour that explains the pass, the QR, the passport, the classes and networking — each step on top of the screen it is describing.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
@@ -2708,17 +2708,17 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>An attendee who has already seen the tour</t>
+          <t>An attendee who has already run the tour</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Sign in again, then press 'Quick tour' in the top bar — try it from the Passport screen, not Home.</t>
+          <t>Press 'Quick tour' again, this time from the Passport screen.</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>It does not open by itself a second time. The button is beside Log out on every attendee screen, and starting it from anywhere returns to step 1 on Home. Back, Next and Skip all work, and Skip counts as seen.</t>
+          <t>It starts again at step 1 on Home, from wherever it was pressed. Back, Next and Skip all work, and it stays closed until asked for again.</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -6504,17 +6504,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Sign-in screen</t>
+          <t>Any sign-in screen, any app</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Look for a Demo / Mock mode switch.</t>
+          <t>Look for a Demo / Mock mode switch, and for any attendee or booth you do not recognise.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>There is none — it was removed so nobody demos fake data at the venue by accident.</t>
+          <t>There is no switch and no invented data anywhere: demo mode and its made-up attendees and booths were removed, so every name on every screen comes from the committee's own sheets.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2750,6 +2750,34 @@
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>ATT-35</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Attendee passport</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Look at the order of the cards.</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>WIT.id is first, then the sponsors, then the booths by number. Placement only — the dashboard's Booth Ranking still counts scans honestly.</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -2801,7 +2801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3346,6 +3346,62 @@
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>BTH-18</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>A booth account that has never signed in</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Sign in at /tenant/login with the committee-issued password.</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>The 'Choose your password' screen opens before anything else — the scanner stays closed until the crew sets a password of their own (8+ characters). The issued password then stops working.</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>BTH-19</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>A booth that already set its own password</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Sign in again with the new password.</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Straight to the scanner — no password screen. The old committee-issued password is refused.</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6941,7 +6997,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, following the stand — Paper.id is on A20, so booth-a20@natcon.id. Alpha leaders holds two stands as one booth, 'A47 &amp; A48', logging in as booth-a47@natcon.id.</t>
+          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, following the stand — Paper.id is on A20, so booth-a20@natcon.id. The seed password only opens the door once: each crew sets their own on first sign-in. Alpha leaders holds two stands as one booth, 'A47 &amp; A48', logging in as booth-a47@natcon.id.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Sign in at /tenant/login with the committee-issued password.</t>
+          <t>Sign in at /tenant/login with the derived first password: company name + booth code, lowercase, letters &amp; digits only (WIT.id at A14 → witida14).</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>login booth-&lt;code&gt;@natcon.id on SEED_PASSWORD, following the stand — Paper.id is on A20, so booth-a20@natcon.id. The seed password only opens the door once: each crew sets their own on first sign-in. Alpha leaders holds two stands as one booth, 'A47 &amp; A48', logging in as booth-a47@natcon.id.</t>
+          <t>login booth-&lt;code&gt;@natcon.id; first password = company name + booth code, lowercase alphanumerics (SSCX International at A1 → sscxinternationala1). It opens the door once — each crew sets their own on first sign-in. Alpha leaders holds two stands as one booth, 'A47 &amp; A48', logging in as booth-a47@natcon.id / alphaleadersa47a48.</t>
         </is>
       </c>
     </row>
@@ -7026,12 +7026,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>booth-b1@natcon.id / SEED_PASSWORD</t>
+          <t>booth-b1@natcon.id / biomedikab1</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Bio Medika · booth B1 — the sheet's own Sponsor divider made it a sponsor</t>
+          <t>Bio Medika · booth B1 — first password follows the same name+booth rule</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -3425,7 +3425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4764,6 +4764,34 @@
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>MD-46</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Admin · an attendee holding a class</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Open their detail page and press Cancel on the registration.</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>The seat frees immediately — the class detail and the attendee's app agree. The desk searches the person, not the class, so cancelling works from here too.</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5951,7 +5979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6354,6 +6382,34 @@
       </c>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>RPT-13</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Reports · Tenant Leads, scans exist</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Press 'Per tenant (no phone)'.</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>natcon2026-leads-per-tenant.xlsx downloads with one sheet per booth: that booth's visitors, chapters, companies and its own notes — and no phone column anywhere. This is the file handed to the tenants.</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6908,7 +6964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7282,6 +7338,23 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Second committee login</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>panitia@natcon.id / SEED_PASSWORD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Same rights as admin — for the desk crew, so the main admin password is never shared</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -2801,7 +2801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Sign in at /tenant/login with the derived first password: company name + booth code, lowercase, letters &amp; digits only (WIT.id at A14 → witida14).</t>
+          <t>Sign in at /tenant/login. Both halves are all lowercase: booth-&lt;code&gt;@natcon.id, and the first password = company name + booth code, letters &amp; digits only (WIT.id at A14 -&gt; booth-a14@natcon.id / witida14).</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -3402,6 +3402,34 @@
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>BTH-20</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>A booth still on the committee's password, signing in on a phone</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Tap 'show password' so the keyboard capitalises, then type the email and first password with a capital first letter (BOOTH-A14@natcon.id / Witida14).</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Still signs in. Generated passwords are all-lowercase, so the capital a phone keyboard adds is accepted while the booth is on that password. After the crew sets their own, case is matched exactly again.</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 32 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; the 769 attendees are seeded too (Data Peserta) and generate the networking tables on the Tables page.</t>
+          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 32 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; the 856 attendees are seeded too (Data Peserta) and generate the networking tables on the Tables page.</t>
         </is>
       </c>
     </row>
@@ -677,6 +677,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1024,6 +1025,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1740,6 +1742,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2820,6 +2823,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3472,6 +3476,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4868,6 +4873,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6026,6 +6032,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6477,6 +6484,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -7059,12 +7067,12 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>already there — 769 from the ticketing export</t>
+          <t>already there — 856 from the ticketing export</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Seeded by migration 0028. Password = chapter + first name, lowercase, no spaces; they must change it on first sign-in.</t>
+          <t>Seeded by migration 0034. Password = chapter + first name, lowercase, no spaces; they must change it on first sign-in. 146 of them have no company on file — the committee's newer export dropped that column.</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7089,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>login booth-&lt;code&gt;@natcon.id; first password = company name + booth code, lowercase alphanumerics (SSCX International at A1 → sscxinternationala1). It opens the door once — each crew sets their own on first sign-in. Alpha leaders holds two stands as one booth, 'A47 &amp; A48', logging in as booth-a47@natcon.id / alphaleadersa47a48.</t>
+          <t>login booth-&lt;code&gt;@natcon.id; first password = company name + booth code, lowercase alphanumerics (SSCX International at A1 -&gt; sscxinternationala1). It opens the door once — each crew sets their own on first sign-in. GrasiaCare holds two stands as one booth, 'A18 &amp; A20' (login booth-a18@natcon.id); ALPHA LEADERS likewise on 'A47 &amp; A48' (booth-a47@natcon.id). Paper.id is on A22.</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7123,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Bio Medika · booth B1 — first password follows the same name+booth rule</t>
+          <t>Bio Medika - booth B1. The four sponsors are the B and C stands: B1, B2, B3, C1.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -677,7 +677,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1006,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1025,7 +1024,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1700,6 +1698,90 @@
       </c>
       <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>ATT-40</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>An attendee signing in for the very first time</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Sign in with the password on the ticket.</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Before anything else: 'Choose your password' AND a data notice with a checkbox — using the app means giving the committee name and email. Save stays disabled until the box is ticked. Nothing else in the app opens until both are done.</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>ATT-41</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>The same attendee signs in again</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Log out, sign in with the new password.</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Straight to the pass. Neither the password screen nor the notice appears again.</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>ATT-42</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>An attendee who set a password before the notice existed</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Sign in.</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>The notice appears alone, headed 'Before you start', with the button reading 'Agree and continue'. No password fields.</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1742,7 +1824,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2823,7 +2904,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3476,7 +3556,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4873,7 +4952,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6032,7 +6110,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6484,7 +6561,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1805,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Shows their company, BNI chapter, business classification and a WhatsApp link with their number.</t>
+          <t>Shows their company, BNI chapter and business classification. NO phone number and no WhatsApp link — not on screen and not in the response the app receives.</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -2862,6 +2862,34 @@
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>ATT-43</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Attendee app · anywhere another person is shown</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Open a networking tablemate, a saved contact's detail, and the class attendee list.</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>No phone or WhatsApp number appears on any of them. Checking the network response shows the field is absent, not merely hidden.</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2885,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3514,6 +3542,34 @@
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>BTH-21</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Booth · a visitor already scanned</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Open Dashboard, tap the visitor, look at the detail card.</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Name, company, chapter, member code and the note — and no phone number, no Call button. A scan means being counted at the stand, not handing over a WhatsApp; follow-up comes from the committee's leads export.</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1782,6 +1782,62 @@
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>AUTH-24</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>A hall of attendees behind one public IP (venue WiFi NAT)</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Have 16+ different attendees sign in from the same network inside a minute.</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>All of them get in — none see 429. A venue is a single NAT, so a per-IP attempt limit would lock the hall out on the morning. One email here belongs to 17 ticket holders; all 17 work.</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>AUTH-25</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>An account that has just been rate-limited</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>After tripping AUTH-23, sign in to a DIFFERENT account from the same network.</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>The other account signs in normally. Only the account under attack is held, and only for a minute.</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -6654,7 +6654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7168,6 +7168,90 @@
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>CC-31</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Deploy · API behind the load balancer, one replica killed mid-traffic</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>With the stack up, send steady traffic and kill one api container (crash it from inside, e.g. kill -9 1).</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>No request fails — the balancer retries on a neighbour. The container comes back on its own via the restart policy. Note: `docker kill` from outside is treated by Docker as an operator stop and will NOT restart; that is expected, not a fault.</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>CC-32</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Deploy · several API instances starting together</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>docker compose down -v, then up with API_REPLICAS=3, and count the seeded data.</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>856 attendees, 36 exhibitors, 95 chapters — seeded ONCE, not once per instance. Migrations run under a Postgres advisory lock; the other instances wait, then skip.</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>CC-33</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Deploy · rate limit with more than one instance</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Send 16 wrong passwords for one account through the balancer, so they spread across replicas.</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Blocked from the 11th. Failures are counted in the database, so the limit is the fleet's — not 10 per container.</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 32 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; the 856 attendees are seeded too (Data Peserta) and generate the networking tables on the Tables page.</t>
+          <t>Admin — admin@natcon.id / SEED_PASSWORD (default natcon2026). The 32 booths, the 4 sponsors and the 4 learning classes are already in a fresh database; the 866 attendees are seeded too (Data Peserta) and generate the networking tables on the Tables page.</t>
         </is>
       </c>
     </row>
@@ -677,6 +677,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1024,6 +1025,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1880,6 +1882,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2988,6 +2991,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3668,6 +3672,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -5064,6 +5069,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6222,6 +6228,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6673,6 +6680,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -7220,7 +7228,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>856 attendees, 36 exhibitors, 95 chapters — seeded ONCE, not once per instance. Migrations run under a Postgres advisory lock; the other instances wait, then skip.</t>
+          <t>866 attendees, 36 exhibitors, 95 chapters — seeded ONCE, not once per instance. Migrations run under a Postgres advisory lock; the other instances wait, then skip.</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr"/>
@@ -7339,12 +7347,12 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>already there — 856 from the ticketing export</t>
+          <t>already there — 866 from the ticketing export</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Seeded by migration 0034. Password = chapter + first name, lowercase, no spaces; they must change it on first sign-in. 146 of them have no company on file — the committee's newer export dropped that column.</t>
+          <t>Seeded by migration 0038. Password = chapter + first name, lowercase, no spaces; they must change it on first sign-in. 156 of them have no company on file — the committee's newer export dropped that column.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -627,7 +627,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Imported attendees sign in with chapter + first name, lowercase, no spaces — e.g. Heritage + Fahmi = heritagefahmi</t>
+          <t>Imported attendees sign in with SEED_PASSWORD (default natcon2026), the same for every account — e.g. Heritage + Fahmi = heritagefahmi</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>On the attendee app sign in with an attendee's email and their generated password (chapter + first name, lowercase, no spaces).</t>
+          <t>On the attendee app sign in with an attendee's email and their generated password (SEED_PASSWORD (default natcon2026), the same for every account).</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Sign in at /tenant/login. Both halves are all lowercase: booth-&lt;code&gt;@natcon.id, and the first password = company name + booth code, letters &amp; digits only (WIT.id at A14 -&gt; booth-a14@natcon.id / witida14).</t>
+          <t>Sign in at /tenant/login. Both halves are all lowercase: booth-&lt;code&gt;@natcon.id, and the first password is SEED_PASSWORD (default natcon2026) — the same one every account starts on. Booth A14 -&gt; booth-a14@natcon.id / natcon2026.</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Tap 'show password' so the keyboard capitalises, then type the email and first password with a capital first letter (BOOTH-A14@natcon.id / Witida14).</t>
+          <t>Tap 'show password' so the keyboard capitalises, then type the email and first password with a capital first letter (BOOTH-A14@natcon.id / Natcon2026).</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Seeded by migration 0038. Password = chapter + first name, lowercase, no spaces; they must change it on first sign-in. 156 of them have no company on file — the committee's newer export dropped that column.</t>
+          <t>Seeded by migration 0038. Password = SEED_PASSWORD (default natcon2026), the same for every account; they must change it on first sign-in. 156 of them have no company on file — the committee's newer export dropped that column.</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>login booth-&lt;code&gt;@natcon.id; first password = company name + booth code, lowercase alphanumerics (SSCX International at A1 -&gt; sscxinternationala1). It opens the door once — each crew sets their own on first sign-in. GrasiaCare holds two stands as one booth, 'A18 &amp; A20' (login booth-a18@natcon.id); ALPHA LEADERS likewise on 'A47 &amp; A48' (booth-a47@natcon.id). Paper.id is on A22.</t>
+          <t>login booth-&lt;code&gt;@natcon.id; first password = SEED_PASSWORD (default natcon2026), the same for every account. It opens the door once — each crew sets their own on first sign-in. GrasiaCare holds two stands as one booth, 'A18 &amp; A20' (login booth-a18@natcon.id); ALPHA LEADERS likewise on 'A47 &amp; A48' (booth-a47@natcon.id). Paper.id is on A22.</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>booth-b1@natcon.id / biomedikab1</t>
+          <t>booth-b1@natcon.id / natcon2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>chapter + first name, lowercase, no spaces</t>
+          <t>SEED_PASSWORD (default natcon2026), the same for every account</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Learning Class tab</t>
+          <t>Learning Session tab</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Reopen Learning Class.</t>
+          <t>Reopen Learning Session.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Logo only — no venue line. The bottom nav reads Home, My QR, Passport, Learning Class, Network, all on one level.</t>
+          <t>Logo only — no venue line. The bottom nav reads Home, My QR, Passport, Learning Session, Network, all on one level.</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Attendee · Learning Class tab</t>
+          <t>Attendee · Learning Session tab</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Learning Classes page</t>
+          <t>Learning Sessions page</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Learning Classes page</t>
+          <t>Learning Sessions page</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Admin · Learning Classes</t>
+          <t>Admin · Learning Sessions</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Admin · Learning Classes</t>
+          <t>Admin · Learning Sessions</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Admin · Learning Classes</t>
+          <t>Admin · Learning Sessions</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Admin · Learning Classes</t>
+          <t>Admin · Learning Sessions</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Admin · Learning Classes</t>
+          <t>Admin · Learning Sessions</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Admin · Learning Classes, rundown has learning blocks</t>
+          <t>Admin · Learning Sessions, rundown has learning blocks</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Admin · Learning Classes</t>
+          <t>Admin · Learning Sessions</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>The day already carries ten draft blocks — nine on 3 September, registration first and the draw last, two of them Learning Class, plus the Gold Club Breakfast under its own 'Friday 4 September' heading. The new block appears as 09:00 – 10:00 · 1 hour · Plenary, and the attendee agenda shows it without a redeploy.</t>
+          <t>The day already carries ten draft blocks — nine on 3 September, registration first and the draw last, two of them Learning Session, plus the Gold Club Breakfast under its own 'Friday 4 September' heading. The new block appears as 09:00 – 10:00 · 1 hour · Plenary, and the attendee agenda shows it without a redeploy.</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr"/>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Put two classes in the 13:00 block and two in the 14:00 block, from the Learning Classes page.</t>
+          <t>Put two classes in the 13:00 block and two in the 14:00 block, from the Learning Sessions page.</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Learning Classes page</t>
+          <t>Learning Sessions page</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Walk the attendee app: Home, My QR, Passport, Learning Class, Network.</t>
+          <t>Walk the attendee app: Home, My QR, Passport, Learning Session, Network.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Seeded only when the schedule is empty; two of them are Learning Class blocks</t>
+          <t>Seeded only when the schedule is empty; two of them are Learning Session blocks</t>
         </is>
       </c>
     </row>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -677,7 +677,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1025,7 +1024,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1882,7 +1880,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2991,7 +2988,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3672,7 +3668,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -5050,7 +5045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5069,7 +5064,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6186,6 +6180,62 @@
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>OPS-21</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard · the morning, before people sign in</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Open the admin Dashboard and read the 'Password Setup' panel.</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>Two bars: attendees and booths, each showing how many have replaced the password the committee handed out. On a fresh database both read 0 and the bar is empty. Every account starts on the same password, so an account nobody has signed into is one anybody with the briefing sheet can sign into — the bar filling up is the day getting safer.</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>OPS-22</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard · somebody sets their own password</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Have one attendee and one booth sign in and choose a password, then reload the Dashboard.</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Both counts rise by one and never fall back — the change is one-way. The bar turns from warning colour once more than half have done it.</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6228,7 +6278,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6680,7 +6729,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>

--- a/docs/qa/natcon2026-qa-scenarios.xlsx
+++ b/docs/qa/natcon2026-qa-scenarios.xlsx
@@ -677,6 +677,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -1024,6 +1025,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1880,6 +1882,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2988,6 +2991,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -3668,6 +3672,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -5064,6 +5069,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6278,6 +6284,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -6729,6 +6736,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
